--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,113 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133988503</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>334612</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6387102</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105373755</v>
+        <v>133988503</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,17 +706,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mattjärnen, Hl</t>
+          <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334822.0565961778</v>
+        <v>334612</v>
       </c>
       <c r="R2" t="n">
-        <v>6387102.339728177</v>
+        <v>6387102</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,39 +770,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133988503</v>
+        <v>105373755</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -818,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>
+          <t>Mattjärnen, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334612</v>
+        <v>334822</v>
       </c>
       <c r="R3" t="n">
         <v>6387102</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133988503</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,8 +886,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105373755</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133988503</v>
+        <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100001</v>
+        <v>3242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>
+          <t>Granndalen Väst, Granndalen Väst, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334612</v>
+        <v>334646</v>
       </c>
       <c r="R2" t="n">
-        <v>6387102</v>
+        <v>6387026</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,33 +786,33 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133988503</t>
+          <t>https://artportalen.se/Sighting/135744747</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105373755</v>
+        <v>133988503</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,17 +823,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mattjärnen, Hl</t>
+          <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334822</v>
+        <v>334612</v>
       </c>
       <c r="R3" t="n">
         <v>6387102</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,16 +887,118 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133988503</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>105373755</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mattjärnen, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>334822</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6387102</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-12-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-12-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/105373755</t>
         </is>
@@ -896,6 +1008,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,6 +1001,123 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/105373755</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135936101</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Granndalen, Granndalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>334570</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6387032</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår av spillkråka</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135936101</t>
         </is>
       </c>
     </row>
@@ -1009,6 +1126,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135936101</v>
       </c>
       <c r="B5" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91988</v>
+        <v>91989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135936101</v>
       </c>
       <c r="B5" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135936101</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135936101</v>
       </c>
       <c r="B5" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>92002</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>92002</v>
+        <v>92009</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135936101</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -1009,7 +1009,7 @@
         <v>135936101</v>
       </c>
       <c r="B5" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
